--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,6 +704,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Korkeakuusikko, Nb</t>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -768,7 +772,11 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128086940</v>
       </c>
       <c r="B2" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128086940</v>
+        <v>128086916</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>871089</v>
+        <v>871085</v>
       </c>
       <c r="R2" t="n">
-        <v>7455011</v>
+        <v>7455004</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,6 +777,520 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128086940</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>871089</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7455011</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128086946</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>871297</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7454685</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128086930</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>871117</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7454950</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128086924</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>871406</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7454681</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128086926</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>871281</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7454706</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35276-2024 artfynd.xlsx
+++ b/artfynd/A 35276-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086916</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086940</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086946</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086930</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086924</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,8 +1321,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128086926</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>